--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$32</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,10 +316,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -358,7 +355,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。</t>
@@ -370,7 +367,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -416,7 +413,7 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
+    <t>含まれている、インラインのリソース</t>
   </si>
   <si>
     <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
@@ -461,7 +458,7 @@
     <t>Media.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
@@ -483,7 +480,7 @@
     <t>製品またはシステムが管理する、施設内で画像（JPEG等）、映像（MPEG等）、音声ファイルなどのメディアを一意に識別するためのID。</t>
   </si>
   <si>
-    <t>"識別子のラベルと使用法によって、どの種類の識別子であるかを判断することができます。"</t>
+    <t>identifierのラベルと使用法によって、どの種類のidentifierであるかを判断することができます。</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -562,7 +559,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>"イベントのライフサイクルの段階を識別するコード。"</t>
+    <t>イベントのライフサイクルの段階を識別するコード。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
@@ -617,37 +614,34 @@
     <t>メディアを取得・撮影した装置（モダリティ）。</t>
   </si>
   <si>
-    <t>使用する場合、ImagingStudy同様”ES”を指定する。</t>
+    <t>使用する場合、ImagingStudy同様”ES”を指定することが望ましい。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>0008,0060 | 0008,1032</t>
+  </si>
+  <si>
+    <t>Media.view</t>
+  </si>
+  <si>
+    <t>メディアのイメージングビュー（例：横方向、前後方向など）。</t>
+  </si>
+  <si>
+    <t>内視鏡では省略してよい。将来的にニーズが出てきた場合には検討する。</t>
   </si>
   <si>
     <t>example</t>
-  </si>
-  <si>
-    <t>画像の種類に関する詳細情報-種類、目的、または生成に使用される機器の種類についての情報。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/media-modality</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>0008,0060 | 0008,1032</t>
-  </si>
-  <si>
-    <t>Media.view</t>
-  </si>
-  <si>
-    <t>メディアのイメージングビュー（例：横方向、前後方向など）。</t>
-  </si>
-  <si>
-    <t>内視鏡では省略してよい。将来的にニーズが出てきた場合には検討する。</t>
   </si>
   <si>
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
@@ -764,7 +758,7 @@
     <t>Media.operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -1092,21 +1086,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1295,7 +1274,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.62109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1309,8 +1288,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.03125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1460,7 +1439,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1581,7 +1560,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -1704,7 +1683,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -1825,7 +1804,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -1948,7 +1927,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2071,7 +2050,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2194,7 +2173,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2317,7 +2296,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2440,7 +2419,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -2565,7 +2544,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -2584,7 +2563,7 @@
         <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>81</v>
@@ -2688,7 +2667,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
@@ -2813,7 +2792,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2938,7 +2917,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -3061,7 +3040,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>181</v>
       </c>
@@ -3186,7 +3165,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -3249,13 +3228,11 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3288,33 +3265,33 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3340,13 +3317,13 @@
         <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3372,14 +3349,14 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
       </c>
@@ -3396,7 +3373,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -3414,30 +3391,30 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
-      <c r="A18" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3451,7 +3428,7 @@
         <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>81</v>
@@ -3460,16 +3437,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3519,7 +3496,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -3534,37 +3511,37 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3583,19 +3560,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3644,7 +3621,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -3659,37 +3636,37 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3708,16 +3685,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3767,7 +3744,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -3782,33 +3759,33 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3831,16 +3808,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3890,7 +3867,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -3908,30 +3885,30 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AP21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3954,16 +3931,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4013,7 +3990,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4028,33 +4005,33 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AO22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4080,13 +4057,13 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4112,14 +4089,14 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4136,7 +4113,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4151,33 +4128,33 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4203,13 +4180,13 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4235,14 +4212,14 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4259,7 +4236,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4277,30 +4254,30 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AQ24" t="s" s="2">
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>261</v>
       </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4323,16 +4300,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4382,7 +4359,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4400,30 +4377,30 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AO25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4446,16 +4423,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4505,7 +4482,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4523,30 +4500,30 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AQ26" t="s" s="2">
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>274</v>
       </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4569,16 +4546,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4628,7 +4605,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4646,30 +4623,30 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4692,16 +4669,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4751,7 +4728,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -4769,30 +4746,30 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4815,16 +4792,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4874,7 +4851,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -4892,7 +4869,7 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
@@ -4910,12 +4887,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4938,16 +4915,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4997,7 +4974,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5015,30 +4992,30 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5061,16 +5038,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5120,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5138,30 +5115,30 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5184,16 +5161,16 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5243,7 +5220,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5258,19 +5235,19 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -5280,24 +5257,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ32">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI31">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -452,7 +452,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Media.modifierExtension</t>

--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -1264,17 +1264,17 @@
   <dimension ref="A1:AQ32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="20.36328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.36328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.62109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="55.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1283,29 +1283,29 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.0390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="103.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="47.82421875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="71.20703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="49.83203125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="61.046875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="42.72265625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -370,7 +370,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -528,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -647,7 +647,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -792,7 +792,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -813,7 +813,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -847,7 +847,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-media-endoscopy.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
